--- a/samples/K_应付票据明细表.xlsx
+++ b/samples/K_应付票据明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,17 +438,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,22 +468,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>收款人</t>
+          <t>收款人全称</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>出票日</t>
+          <t>出票日期</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>到期日</t>
+          <t>到期日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面额</t>
+          <t>票面金额</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -487,6 +492,26 @@
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>保证金金额</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>是否函证</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>函证结果</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -495,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>YJ-001</t>
+          <t>YP-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -505,20 +530,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>重庆钢铁设备</t>
+          <t>重庆钢铁股份有限公司</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>500000</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -526,12 +551,34 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>已兑付</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>已到期兑付</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>YJ-002</t>
+          <t>YP-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,64 +588,224 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>华为技术</t>
+          <t>华为技术有限公司</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>400000</v>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>380000</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="3" t="n">
+        <v>114000</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>已兑付</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>已到期兑付</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>YJ-003</t>
+          <t>YP-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>商承</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>湖北双环科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>265000</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>已兑付</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>已到期兑付</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>YP-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>银承</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>重庆建工</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>重庆建工集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>186000</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>未到期</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>YP-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>商承</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>中石化重庆分公司</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>未到期</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
